--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 39628-2026 artfynd.xlsx
+++ b/artfynd/A 39628-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136548018</v>
       </c>
       <c r="B3" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136548828</v>
       </c>
       <c r="B4" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136550453</v>
       </c>
       <c r="B5" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
